--- a/rules/CORE-000195/negative/01/data/unit-test-coreid-CG0338-negative 1.xlsx
+++ b/rules/CORE-000195/negative/01/data/unit-test-coreid-CG0338-negative 1.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -49,6 +49,10 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -74,7 +78,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -115,12 +119,6 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -141,18 +139,17 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,10 +492,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -522,10 +519,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>Adverse Events</v>
       </c>
     </row>
@@ -538,7 +535,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -561,175 +558,135 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>AESCAT</v>
       </c>
-      <c r="F2" s="2" t="str">
-        <v>INJECTION SITE REACTION</v>
+      <c r="F2" s="4" t="str">
+        <v>SAME TEXT CASE</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <v>ae.xpt</v>
+      </c>
+      <c r="C3" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D3" s="4">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <v>AEDECOD</v>
+      </c>
+      <c r="F3" s="4" t="str">
+        <v>SAME TEXT CASE</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B4" s="4" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C4" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="4">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E4" s="4" t="str">
         <v>AESCAT</v>
       </c>
-      <c r="F3" s="2" t="str">
-        <v>Injection Site Reaction</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
+      <c r="F4" s="4">
+        <v>123456789</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <v>ae.xpt</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D5" s="4">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <v>AEDECOD</v>
+      </c>
+      <c r="F5" s="4">
+        <v>123456789</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="str">
+      <c r="B6" s="4" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="C4" s="2" t="str">
+      <c r="C6" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D4" s="2">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="str">
+      <c r="D6" s="4">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="str">
         <v>AESCAT</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <v>CHEST DISCOMFORT</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="str">
+      <c r="F6" s="4" t="str">
+        <v>Different Text Case</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="C5" s="2" t="str">
+      <c r="C7" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D7" s="4">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <v>AESCAT</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v>Headache</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D6" s="2">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v>AESCAT</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v>MYOCARDIAL INFARCTION</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D7" s="2">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v>AESCAT</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <v>PARAESTHESIA ORAL</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D8" s="2">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v>AESCAT</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <v>NASOPHARYNGITIS</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="C9" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D9" s="2">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v>AESCAT</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <v>Supraventricular Extrasystoles</v>
+      <c r="E7" s="4" t="str">
+        <v>AEDECOD</v>
+      </c>
+      <c r="F7" s="4" t="str">
+        <v>DIFFERENT TEXT CASE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -755,378 +712,239 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="6" t="str">
         <v>Reported Term for the Adverse Event</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="6" t="str">
         <v>Dictionary-Derived Term</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="7" t="str">
         <v>Subcategory for Adverse Event</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="str">
+      <c r="A3" s="6" t="str">
         <v>Char</v>
       </c>
-      <c r="B3" s="5" t="str">
+      <c r="B3" s="6" t="str">
         <v>Char</v>
       </c>
-      <c r="C3" s="5" t="str">
+      <c r="C3" s="6" t="str">
         <v>Char</v>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="6" t="str">
         <v>Char</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="6" t="str">
         <v>Char</v>
       </c>
-      <c r="G3" s="6" t="str">
+      <c r="G3" s="7" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="6">
         <v>200</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>200</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="7">
         <v>200</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="4" t="str">
         <v>AE</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="4" t="str">
         <v>CDISC005</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="4" t="str">
         <v>INJECTION SITE REACTION</v>
       </c>
-      <c r="F5" s="7" t="str">
-        <v>INJECTION SITE REACTION</v>
+      <c r="F5" s="8" t="str">
+        <v>SAME TEXT CASE</v>
       </c>
       <c r="G5" s="8" t="str">
-        <v>INJECTION SITE REACTION</v>
+        <v>SAME TEXT CASE</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="str">
+      <c r="A6" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="4" t="str">
         <v>AE</v>
       </c>
-      <c r="C6" s="7" t="str">
+      <c r="C6" s="4" t="str">
         <v>CDISC005</v>
       </c>
-      <c r="D6" s="7">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7" t="str">
-        <v>INJECTION SITE REACTION</v>
-      </c>
-      <c r="F6" s="7" t="str">
-        <v>INJECTION SITE REACTION</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <v>Injection Site Reaction</v>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <v>Foo</v>
+      </c>
+      <c r="F6" s="8">
+        <v>123456789</v>
+      </c>
+      <c r="G6" s="8">
+        <v>123456789</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="4" t="str">
         <v>AE</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="4" t="str">
         <v>CDISC005</v>
       </c>
-      <c r="D7" s="7">
-        <v>5</v>
-      </c>
-      <c r="E7" s="7" t="str">
-        <v>CHEST DISCOMFORT</v>
-      </c>
-      <c r="F7" s="7" t="str">
-        <v>CHEST DISCOMFORT</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <v>CHEST DISCOMFORT</v>
+      <c r="D7" s="4">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <v>COUGH</v>
+      </c>
+      <c r="F7" s="4" t="str">
+        <v>Foo</v>
+      </c>
+      <c r="G7" s="4" t="str">
+        <v>Bar</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="4" t="str">
         <v>AE</v>
       </c>
-      <c r="C8" s="7" t="str">
-        <v>CDISC005</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="4" t="str">
+        <v>CDISC016</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <v>SUPRAVENTRICULAR EXTRASYSTOLES</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <v>DIFFERENT TEXT CASE</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <v>Different Text Case</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <v>CDISC016</v>
+      </c>
+      <c r="D9" s="4">
         <v>6</v>
       </c>
-      <c r="E8" s="7" t="str">
-        <v>HEADACHE</v>
-      </c>
-      <c r="F8" s="7" t="str">
-        <v>HEADACHE</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <v>Headache</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B9" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C9" s="7" t="str">
-        <v>CDISC005</v>
-      </c>
-      <c r="D9" s="7">
-        <v>7</v>
-      </c>
-      <c r="E9" s="7" t="str">
-        <v>COUGH</v>
-      </c>
-      <c r="F9" s="7" t="str">
-        <v>COUGH</v>
-      </c>
-      <c r="G9" s="2" t="str">
-        <v>Coughing</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B10" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C10" s="7" t="str">
-        <v>CDISC013</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7" t="str">
-        <v>MYOCARDIAL INFARCTION</v>
-      </c>
-      <c r="F10" s="7" t="str">
-        <v>MYOCARDIAL INFARCTION</v>
-      </c>
-      <c r="G10" s="9" t="str">
-        <v>MYOCARDIAL INFARCTION</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B11" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C11" s="7" t="str">
-        <v>CDISC016</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="str">
-        <v>PARAESTHESIA ORAL</v>
-      </c>
-      <c r="F11" s="7" t="str">
-        <v>PARAESTHESIA ORAL</v>
-      </c>
-      <c r="G11" s="9" t="str">
-        <v>PARAESTHESIA ORAL</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B12" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C12" s="7" t="str">
-        <v>CDISC016</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2</v>
-      </c>
-      <c r="E12" s="7" t="str">
-        <v>NASOPHARYNGITIS</v>
-      </c>
-      <c r="F12" s="7" t="str">
-        <v>NASOPHARYNGITIS</v>
-      </c>
-      <c r="G12" s="9" t="str">
-        <v>NASOPHARYNGITIS</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B13" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C13" s="7" t="str">
-        <v>CDISC016</v>
-      </c>
-      <c r="D13" s="7">
-        <v>3</v>
-      </c>
-      <c r="E13" s="7" t="str">
-        <v>SUPRAVENTRICULAR EXTRASYSTOLES</v>
-      </c>
-      <c r="F13" s="7" t="str">
-        <v>SUPRAVENTRICULAR EXTRASYSTOLES</v>
-      </c>
-      <c r="G13" s="10" t="str">
-        <v>Supraventricular Extrasystoles</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B14" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C14" s="7" t="str">
-        <v>CDISC016</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4</v>
-      </c>
-      <c r="E14" s="7" t="str">
-        <v>Rash Pruritic</v>
-      </c>
-      <c r="F14" s="7" t="str">
-        <v>RASH PRURITIC</v>
-      </c>
-      <c r="G14" s="2" t="str">
-        <v>RASH</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B15" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C15" s="7" t="str">
-        <v>CDISC016</v>
-      </c>
-      <c r="D15" s="7">
-        <v>5</v>
-      </c>
-      <c r="E15" s="7" t="str">
-        <v>VENTRICULAR EXTRASYSTOLES</v>
-      </c>
-      <c r="F15" s="7" t="str">
-        <v>VENTRICULAR EXTRASYSTOLES</v>
-      </c>
-      <c r="G15" s="2" t="str" xml:space="preserve">
+      <c r="E9" s="4" t="str">
+        <v>CONJUNCTIVAL HAEMORRHAGE</v>
+      </c>
+      <c r="F9" s="4" t="str">
+        <v>Non-blank vs blank</v>
+      </c>
+      <c r="G9" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" s="7" t="str">
+    <row r="10">
+      <c r="A10" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B16" s="7" t="str">
+      <c r="B10" s="4" t="str">
         <v>AE</v>
       </c>
-      <c r="C16" s="7" t="str">
+      <c r="C10" s="4" t="str">
         <v>CDISC016</v>
       </c>
-      <c r="D16" s="7">
-        <v>6</v>
-      </c>
-      <c r="E16" s="7" t="str">
-        <v>CONJUNCTIVAL HAEMORRHAGE</v>
-      </c>
-      <c r="F16" s="7" t="str">
-        <v>Conjunctival Haemorrhage</v>
-      </c>
-      <c r="G16" s="2" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="str">
+      <c r="D10" s="4">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <v>Blah</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B17" s="7" t="str">
+      <c r="B11" s="4" t="str">
         <v>AE</v>
       </c>
-      <c r="C17" s="7" t="str">
+      <c r="C11" s="4" t="str">
         <v>CDISC016</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D11" s="4">
         <v>7</v>
       </c>
-      <c r="E17" s="7" t="str">
+      <c r="E11" s="4" t="str">
         <v>CERUMEN IMPACTION</v>
       </c>
-      <c r="F17" s="7" t="str">
+      <c r="F11" s="4" t="str">
         <v/>
       </c>
-      <c r="G17" s="2" t="str">
-        <v>Some random AESCAT</v>
+      <c r="G11" s="4" t="str">
+        <v>Blank vs. non-blank</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
   </ignoredErrors>
 </worksheet>
 </file>